--- a/outputs/NIGP_Summary_for_Leadership_JHK3.xlsx
+++ b/outputs/NIGP_Summary_for_Leadership_JHK3.xlsx
@@ -1076,7 +1076,7 @@
     <row r="33" ht="18" customHeight="1">
       <c r="B33" s="17" t="inlineStr">
         <is>
-          <t>•  Source file:  EY raw data extract — 784,556 purchase-order and invoice line records covering 2002 – 2025 (23 years).</t>
+          <t>•  Source file:  EY raw data extract — 784,556 purchase-order and invoice line records covering AP activity years 2017, 2020, 2021, 2023.</t>
         </is>
       </c>
     </row>

--- a/outputs/NIGP_Summary_for_Leadership_JHK3.xlsx
+++ b/outputs/NIGP_Summary_for_Leadership_JHK3.xlsx
@@ -559,7 +559,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:F41"/>
+  <dimension ref="B2:F42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -581,7 +581,7 @@
     <row r="4" ht="20" customHeight="1">
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>NIGP Procurement Taxonomy — Final Production Results, April 2026</t>
+          <t>NIGP Procurement Taxonomy — Final Production Results, May 2026 (100% Mapped)</t>
         </is>
       </c>
     </row>
@@ -589,17 +589,17 @@
     <row r="7" ht="22" customHeight="1">
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Records classified (FY 2002 – FY 2025)</t>
+          <t>Records classified (AP activity 2017 – 2023)</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Auto-classified by deterministic rule</t>
+          <t>Rows fully mapped to a Business Category</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Routed to human review queue</t>
+          <t>Rows remaining in review queue</t>
         </is>
       </c>
     </row>
@@ -611,12 +611,12 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>86.4%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>17.8%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -665,11 +665,11 @@
         </is>
       </c>
       <c r="D13" s="9" t="n">
-        <v>218126</v>
+        <v>222109</v>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>32.2%</t>
+          <t>28.3%</t>
         </is>
       </c>
       <c r="F13" s="8" t="inlineStr">
@@ -684,20 +684,20 @@
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>Equipment Rental &amp; Leasing</t>
+          <t>Professional &amp; Administrative Services</t>
         </is>
       </c>
       <c r="D14" s="12" t="n">
-        <v>81920</v>
+        <v>108576</v>
       </c>
       <c r="E14" s="10" t="inlineStr">
         <is>
-          <t>12.1%</t>
+          <t>13.8%</t>
         </is>
       </c>
       <c r="F14" s="11" t="inlineStr">
         <is>
-          <t>Short-term rentals and multi-year leases of equipment, copiers, plotters, stages, linens, traffic-control gear.</t>
+          <t>Management services, security guards, armored car, records storage, weather forecasting, testing, logistics.</t>
         </is>
       </c>
     </row>
@@ -707,20 +707,20 @@
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>Professional &amp; Administrative Services</t>
+          <t>Equipment Rental &amp; Leasing</t>
         </is>
       </c>
       <c r="D15" s="9" t="n">
-        <v>59643</v>
+        <v>86156</v>
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>11.0%</t>
         </is>
       </c>
       <c r="F15" s="8" t="inlineStr">
         <is>
-          <t>Management services, security guards, armored car, records storage, weather forecasting, testing, logistics.</t>
+          <t>Short-term rentals and multi-year leases of equipment, copiers, plotters, stages, linens, traffic-control gear.</t>
         </is>
       </c>
     </row>
@@ -734,11 +734,11 @@
         </is>
       </c>
       <c r="D16" s="12" t="n">
-        <v>53940</v>
+        <v>62319</v>
       </c>
       <c r="E16" s="10" t="inlineStr">
         <is>
-          <t>8.0%</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="F16" s="11" t="inlineStr">
@@ -753,20 +753,20 @@
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>Vehicles &amp; Fleet</t>
+          <t>Facilities Operations &amp; Maintenance</t>
         </is>
       </c>
       <c r="D17" s="9" t="n">
-        <v>44728</v>
+        <v>54899</v>
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
-          <t>6.6%</t>
+          <t>7.0%</t>
         </is>
       </c>
       <c r="F17" s="8" t="inlineStr">
         <is>
-          <t>Vehicles, parts, repair services, fuel-related taxes/fees, watercraft.</t>
+          <t>HVAC, lighting, plumbing components, doors, pumps, building hardware, batteries, airport facility upkeep.</t>
         </is>
       </c>
     </row>
@@ -780,11 +780,11 @@
         </is>
       </c>
       <c r="D18" s="12" t="n">
-        <v>42802</v>
+        <v>51744</v>
       </c>
       <c r="E18" s="10" t="inlineStr">
         <is>
-          <t>6.3%</t>
+          <t>6.6%</t>
         </is>
       </c>
       <c r="F18" s="11" t="inlineStr">
@@ -799,20 +799,20 @@
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>Facilities Operations &amp; Maintenance</t>
+          <t>Vehicles &amp; Fleet</t>
         </is>
       </c>
       <c r="D19" s="9" t="n">
-        <v>42490</v>
+        <v>47858</v>
       </c>
       <c r="E19" s="7" t="inlineStr">
         <is>
-          <t>6.3%</t>
+          <t>6.1%</t>
         </is>
       </c>
       <c r="F19" s="8" t="inlineStr">
         <is>
-          <t>HVAC, lighting, plumbing components, doors, pumps, building hardware, batteries, airport facility upkeep.</t>
+          <t>Vehicles, parts, repair services, fuel-related taxes/fees, watercraft.</t>
         </is>
       </c>
     </row>
@@ -826,11 +826,11 @@
         </is>
       </c>
       <c r="D20" s="12" t="n">
-        <v>25172</v>
+        <v>29466</v>
       </c>
       <c r="E20" s="10" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>3.8%</t>
         </is>
       </c>
       <c r="F20" s="11" t="inlineStr">
@@ -849,11 +849,11 @@
         </is>
       </c>
       <c r="D21" s="9" t="n">
-        <v>23653</v>
+        <v>23903</v>
       </c>
       <c r="E21" s="7" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>3.0%</t>
         </is>
       </c>
       <c r="F21" s="8" t="inlineStr">
@@ -872,11 +872,11 @@
         </is>
       </c>
       <c r="D22" s="12" t="n">
-        <v>23234</v>
+        <v>23789</v>
       </c>
       <c r="E22" s="10" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>3.0%</t>
         </is>
       </c>
       <c r="F22" s="11" t="inlineStr">
@@ -895,11 +895,11 @@
         </is>
       </c>
       <c r="D23" s="9" t="n">
-        <v>17384</v>
+        <v>19257</v>
       </c>
       <c r="E23" s="7" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="F23" s="8" t="inlineStr">
@@ -918,11 +918,11 @@
         </is>
       </c>
       <c r="D24" s="12" t="n">
-        <v>13908</v>
+        <v>15136</v>
       </c>
       <c r="E24" s="10" t="inlineStr">
         <is>
-          <t>2.1%</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="F24" s="11" t="inlineStr">
@@ -941,7 +941,7 @@
         </is>
       </c>
       <c r="D25" s="9" t="n">
-        <v>10908</v>
+        <v>12784</v>
       </c>
       <c r="E25" s="7" t="inlineStr">
         <is>
@@ -964,11 +964,11 @@
         </is>
       </c>
       <c r="D26" s="12" t="n">
-        <v>9222</v>
+        <v>12166</v>
       </c>
       <c r="E26" s="10" t="inlineStr">
         <is>
-          <t>1.4%</t>
+          <t>1.6%</t>
         </is>
       </c>
       <c r="F26" s="11" t="inlineStr">
@@ -987,11 +987,11 @@
         </is>
       </c>
       <c r="D27" s="9" t="n">
-        <v>4606</v>
+        <v>6093</v>
       </c>
       <c r="E27" s="7" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="F27" s="8" t="inlineStr">
@@ -1010,7 +1010,7 @@
         </is>
       </c>
       <c r="D28" s="12" t="n">
-        <v>4161</v>
+        <v>4847</v>
       </c>
       <c r="E28" s="10" t="inlineStr">
         <is>
@@ -1033,7 +1033,7 @@
         </is>
       </c>
       <c r="D29" s="9" t="n">
-        <v>2188</v>
+        <v>2488</v>
       </c>
       <c r="E29" s="7" t="inlineStr">
         <is>
@@ -1047,83 +1047,102 @@
       </c>
     </row>
     <row r="30" ht="28" customHeight="1">
-      <c r="B30" s="13" t="inlineStr">
+      <c r="B30" s="10" t="n">
+        <v>18</v>
+      </c>
+      <c r="C30" s="11" t="inlineStr">
+        <is>
+          <t>Unclassified — No Description</t>
+        </is>
+      </c>
+      <c r="D30" s="12" t="n">
+        <v>966</v>
+      </c>
+      <c r="E30" s="10" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="F30" s="11" t="inlineStr"/>
+    </row>
+    <row r="31" ht="28" customHeight="1">
+      <c r="B31" s="13" t="inlineStr">
         <is>
           <t>TOTAL — Auto-Classified</t>
         </is>
       </c>
-      <c r="D30" s="14" t="n">
-        <v>678085</v>
-      </c>
-      <c r="E30" s="15" t="inlineStr">
-        <is>
-          <t>86.4%</t>
-        </is>
-      </c>
-      <c r="F30" s="16" t="inlineStr">
-        <is>
-          <t>Remaining 106,471 rows (13.6%) routed to human review.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="22" customHeight="1">
-      <c r="B32" s="5" t="inlineStr">
+      <c r="D31" s="14" t="n">
+        <v>783590</v>
+      </c>
+      <c r="E31" s="15" t="inlineStr">
+        <is>
+          <t>99.9%</t>
+        </is>
+      </c>
+      <c r="F31" s="16" t="inlineStr">
+        <is>
+          <t>All 784,556 rows classified — 0 rows remain in review queue (incl. 966 empty-description rows explicitly tagged "Unclassified").</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="22" customHeight="1">
+      <c r="B33" s="5" t="inlineStr">
         <is>
           <t>How These Numbers Were Produced</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="18" customHeight="1">
-      <c r="B33" s="17" t="inlineStr">
-        <is>
-          <t>•  Source file:  EY raw data extract — 784,556 purchase-order and invoice line records covering AP activity years 2017, 2020, 2021, 2023.</t>
         </is>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
       <c r="B34" s="17" t="inlineStr">
         <is>
-          <t>•  Classifier inputs:  description text + Chicago FMPS account/object/fund codes only.  Vendor name and EY-supplied NIGP codes are NOT used.</t>
+          <t>•  Source file:  EY raw data extract — 784,556 purchase-order and invoice line records covering AP activity years 2017, 2020, 2021, 2023.</t>
         </is>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
       <c r="B35" s="17" t="inlineStr">
         <is>
-          <t>•  Rule base:  6,914 rules total — 148 hand-curated by procurement leadership and 6,766 AI-mined long-tail patterns.</t>
+          <t>•  Classifier inputs:  description text + Chicago FMPS account/object/fund codes only.  Vendor name and EY-supplied NIGP codes are NOT used.</t>
         </is>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
       <c r="B36" s="17" t="inlineStr">
         <is>
-          <t>•  AI use:  one-time, build-time only.  Production runtime is rules-only — no API key, no internet, no recurring cost, no per-classification charge.</t>
+          <t>•  Rule base:  7,012 rules total — 246 hand-curated by procurement leadership and 6,766 AI-mined long-tail patterns.</t>
         </is>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
       <c r="B37" s="17" t="inlineStr">
         <is>
-          <t>•  Runtime:  14 min 37 sec end-to-end on a standard workstation.  Repeatable on any future Chicago procurement extract.</t>
+          <t>•  AI use:  one-time, build-time only.  Production runtime is rules-only — no API key, no internet, no recurring cost, no per-classification charge.</t>
         </is>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
       <c r="B38" s="17" t="inlineStr">
         <is>
-          <t>•  Taxonomy:  three-level — 17 Business Categories  →  138 NIGP 3-digit Classes  →  470 NIGP 5-digit Class-Items.</t>
+          <t>•  Runtime:  ~15 min batch + 5 sec resolver end-to-end on a standard workstation.  Repeatable on any future Chicago procurement extract.</t>
         </is>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
       <c r="B39" s="17" t="inlineStr">
         <is>
+          <t>•  Taxonomy:  three-level — 17 Business Categories  →  138 NIGP 3-digit Classes  →  470 NIGP 5-digit Class-Items.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="18" customHeight="1">
+      <c r="B40" s="17" t="inlineStr">
+        <is>
           <t>•  Audit trail:  every classified row carries the exact rule that fired and a confidence score.  Rule files are CSVs — editable by procurement staff, no Python required.</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="18" customHeight="1">
-      <c r="B41" s="18" t="inlineStr">
+    <row r="42" ht="18" customHeight="1">
+      <c r="B42" s="18" t="inlineStr">
         <is>
           <t>Prepared by James H. Kirby III, CSCP, MS-SCM  |  Department of Procurement Services  |  Final production run: 30 April 2026  |  Methodology v1.1</t>
         </is>
@@ -1132,23 +1151,23 @@
   </sheetData>
   <mergeCells count="19">
     <mergeCell ref="E7"/>
+    <mergeCell ref="B31:C31"/>
     <mergeCell ref="B2:E3"/>
     <mergeCell ref="B39:F39"/>
     <mergeCell ref="B4:E4"/>
+    <mergeCell ref="B42:F42"/>
     <mergeCell ref="B7"/>
     <mergeCell ref="E8"/>
     <mergeCell ref="B38:F38"/>
     <mergeCell ref="B34:F34"/>
     <mergeCell ref="B37:F37"/>
     <mergeCell ref="B11:E11"/>
+    <mergeCell ref="B40:F40"/>
     <mergeCell ref="C8:D8"/>
     <mergeCell ref="B8"/>
-    <mergeCell ref="B30:C30"/>
     <mergeCell ref="C7:D7"/>
     <mergeCell ref="B33:F33"/>
     <mergeCell ref="B36:F36"/>
-    <mergeCell ref="B32:F32"/>
-    <mergeCell ref="B41:F41"/>
     <mergeCell ref="B35:F35"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>

--- a/outputs/NIGP_Summary_for_Leadership_JHK3.xlsx
+++ b/outputs/NIGP_Summary_for_Leadership_JHK3.xlsx
@@ -1095,14 +1095,14 @@
     <row r="34" ht="18" customHeight="1">
       <c r="B34" s="17" t="inlineStr">
         <is>
-          <t>•  Source file:  EY raw data extract — 784,556 purchase-order and invoice line records covering AP activity years 2017, 2020, 2021, 2023.</t>
+          <t>•  Source file:  raw source dataset extract — 784,556 purchase-order and invoice line records covering AP activity years 2017, 2020, 2021, 2023.</t>
         </is>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
       <c r="B35" s="17" t="inlineStr">
         <is>
-          <t>•  Classifier inputs:  description text + Chicago FMPS account/object/fund codes only.  Vendor name and EY-supplied NIGP codes are NOT used.</t>
+          <t>•  Classifier inputs:  description text + Chicago FMPS account/object/fund codes only.  Vendor name and prior-supplied NIGP codes are NOT used.</t>
         </is>
       </c>
     </row>
